--- a/public/mesai_sablon.xlsx
+++ b/public/mesai_sablon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\izin-otomasyon\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B411597-AB4B-4AD8-AA7D-3D79E34583DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B928DDD-9A88-42B3-A9F7-8C4206D05388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="HAZİRAN-2026" sheetId="117" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HAZİRAN-2026'!$A$4:$AO$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HAZİRAN-2026'!$A$4:$AN$8</definedName>
     <definedName name="Print_Area_0" localSheetId="0">'HAZİRAN-2026'!$A$1:$AN$15</definedName>
     <definedName name="Print_Titles_0" localSheetId="0">'HAZİRAN-2026'!$1:$7</definedName>
     <definedName name="Print_Titles_0_0" localSheetId="0">'HAZİRAN-2026'!$1:$7</definedName>
@@ -414,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -534,7 +534,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -563,50 +562,50 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -961,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDEE2F40-3925-4217-A50B-CA2854E653BC}">
-  <dimension ref="A1:AO1315"/>
+  <dimension ref="A1:AN1315"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="42" customWidth="1"/>
@@ -970,285 +969,285 @@
     <col min="4" max="4" width="14.140625" style="44" customWidth="1"/>
     <col min="5" max="5" width="24.7109375" style="44" customWidth="1"/>
     <col min="6" max="6" width="18" style="42" customWidth="1"/>
-    <col min="7" max="9" width="3.42578125" style="52" customWidth="1"/>
+    <col min="7" max="9" width="3.42578125" style="51" customWidth="1"/>
     <col min="10" max="14" width="3.42578125" customWidth="1"/>
-    <col min="15" max="16" width="3.42578125" style="52" customWidth="1"/>
+    <col min="15" max="16" width="3.42578125" style="51" customWidth="1"/>
     <col min="17" max="21" width="3.42578125" customWidth="1"/>
-    <col min="22" max="23" width="3.42578125" style="52" customWidth="1"/>
+    <col min="22" max="23" width="3.42578125" style="51" customWidth="1"/>
     <col min="24" max="24" width="3.42578125" customWidth="1"/>
-    <col min="25" max="25" width="3.42578125" style="52" customWidth="1"/>
+    <col min="25" max="25" width="3.42578125" style="51" customWidth="1"/>
     <col min="26" max="28" width="3.42578125" customWidth="1"/>
-    <col min="29" max="36" width="3.42578125" style="52" customWidth="1"/>
+    <col min="29" max="36" width="3.42578125" style="51" customWidth="1"/>
     <col min="37" max="37" width="3.42578125" customWidth="1"/>
-    <col min="38" max="253" width="8.140625" customWidth="1"/>
-    <col min="254" max="1021" width="8.5703125" customWidth="1"/>
+    <col min="38" max="252" width="8.140625" customWidth="1"/>
+    <col min="253" max="1020" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70"/>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="70"/>
-      <c r="T1" s="70"/>
-      <c r="U1" s="70"/>
-      <c r="V1" s="70"/>
-      <c r="W1" s="70"/>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="70"/>
-      <c r="Z1" s="70"/>
-      <c r="AA1" s="70"/>
-      <c r="AB1" s="70"/>
-      <c r="AC1" s="70"/>
-      <c r="AD1" s="70"/>
-      <c r="AE1" s="70"/>
-      <c r="AF1" s="70"/>
-      <c r="AG1" s="70"/>
-      <c r="AH1" s="70"/>
-      <c r="AI1" s="70"/>
-      <c r="AJ1" s="70"/>
-      <c r="AK1" s="70"/>
-      <c r="AL1" s="70"/>
-      <c r="AM1" s="70"/>
-      <c r="AN1" s="70"/>
+    <row r="1" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="61"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
+      <c r="AB1" s="61"/>
+      <c r="AC1" s="61"/>
+      <c r="AD1" s="61"/>
+      <c r="AE1" s="61"/>
+      <c r="AF1" s="61"/>
+      <c r="AG1" s="61"/>
+      <c r="AH1" s="61"/>
+      <c r="AI1" s="61"/>
+      <c r="AJ1" s="61"/>
+      <c r="AK1" s="61"/>
+      <c r="AL1" s="61"/>
+      <c r="AM1" s="61"/>
+      <c r="AN1" s="61"/>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="70"/>
-      <c r="U2" s="70"/>
-      <c r="V2" s="70"/>
-      <c r="W2" s="70"/>
-      <c r="X2" s="70"/>
-      <c r="Y2" s="70"/>
-      <c r="Z2" s="70"/>
-      <c r="AA2" s="70"/>
-      <c r="AB2" s="70"/>
-      <c r="AC2" s="70"/>
-      <c r="AD2" s="70"/>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="70"/>
-      <c r="AJ2" s="70"/>
-      <c r="AK2" s="70"/>
-      <c r="AL2" s="70"/>
-      <c r="AM2" s="70"/>
-      <c r="AN2" s="70"/>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="61"/>
+      <c r="Z2" s="61"/>
+      <c r="AA2" s="61"/>
+      <c r="AB2" s="61"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="61"/>
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="61"/>
+      <c r="AG2" s="61"/>
+      <c r="AH2" s="61"/>
+      <c r="AI2" s="61"/>
+      <c r="AJ2" s="61"/>
+      <c r="AK2" s="61"/>
+      <c r="AL2" s="61"/>
+      <c r="AM2" s="61"/>
+      <c r="AN2" s="61"/>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="32"/>
       <c r="B3" s="33"/>
       <c r="C3" s="34"/>
       <c r="D3" s="34"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
       <c r="T3" s="11"/>
       <c r="U3" s="11"/>
-      <c r="V3" s="48"/>
-      <c r="W3" s="48"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
       <c r="X3" s="11"/>
-      <c r="Y3" s="48"/>
+      <c r="Y3" s="47"/>
       <c r="Z3" s="11"/>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="48"/>
-      <c r="AF3" s="48"/>
-      <c r="AG3" s="48"/>
-      <c r="AH3" s="48"/>
-      <c r="AI3" s="48"/>
-      <c r="AJ3" s="48"/>
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="47"/>
+      <c r="AE3" s="47"/>
+      <c r="AF3" s="47"/>
+      <c r="AG3" s="47"/>
+      <c r="AH3" s="47"/>
+      <c r="AI3" s="47"/>
+      <c r="AJ3" s="47"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
       <c r="AM3" s="11"/>
       <c r="AN3" s="46"/>
     </row>
-    <row r="4" spans="1:41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+    <row r="4" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="72" t="s">
+      <c r="B4" s="62"/>
+      <c r="C4" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
       <c r="F4" s="37"/>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="74"/>
-      <c r="Z4" s="74"/>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="74"/>
-      <c r="AC4" s="74"/>
-      <c r="AD4" s="74"/>
-      <c r="AE4" s="74"/>
-      <c r="AF4" s="74"/>
-      <c r="AG4" s="74"/>
-      <c r="AH4" s="74"/>
-      <c r="AI4" s="74"/>
-      <c r="AJ4" s="74"/>
-      <c r="AK4" s="74"/>
-      <c r="AL4" s="75"/>
-      <c r="AM4" s="75"/>
-      <c r="AN4" s="75"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="65"/>
+      <c r="AF4" s="65"/>
+      <c r="AG4" s="65"/>
+      <c r="AH4" s="65"/>
+      <c r="AI4" s="65"/>
+      <c r="AJ4" s="65"/>
+      <c r="AK4" s="65"/>
+      <c r="AL4" s="66"/>
+      <c r="AM4" s="66"/>
+      <c r="AN4" s="66"/>
     </row>
-    <row r="5" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
-      <c r="B5" s="71"/>
-      <c r="C5" s="76" t="s">
+    <row r="5" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="62"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
       <c r="F5" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
-      <c r="W5" s="74"/>
-      <c r="X5" s="74"/>
-      <c r="Y5" s="74"/>
-      <c r="Z5" s="74"/>
-      <c r="AA5" s="74"/>
-      <c r="AB5" s="74"/>
-      <c r="AC5" s="74"/>
-      <c r="AD5" s="74"/>
-      <c r="AE5" s="74"/>
-      <c r="AF5" s="74"/>
-      <c r="AG5" s="74"/>
-      <c r="AH5" s="74"/>
-      <c r="AI5" s="74"/>
-      <c r="AJ5" s="74"/>
-      <c r="AK5" s="74"/>
-      <c r="AL5" s="75"/>
-      <c r="AM5" s="75"/>
-      <c r="AN5" s="75"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="65"/>
+      <c r="AF5" s="65"/>
+      <c r="AG5" s="65"/>
+      <c r="AH5" s="65"/>
+      <c r="AI5" s="65"/>
+      <c r="AJ5" s="65"/>
+      <c r="AK5" s="65"/>
+      <c r="AL5" s="66"/>
+      <c r="AM5" s="66"/>
+      <c r="AN5" s="66"/>
     </row>
-    <row r="6" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66" t="s">
+    <row r="6" spans="1:40" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
       <c r="E6" s="39"/>
       <c r="F6" s="45"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="67"/>
-      <c r="X6" s="67"/>
-      <c r="Y6" s="67"/>
-      <c r="Z6" s="67"/>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="67"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="67"/>
-      <c r="AG6" s="67"/>
-      <c r="AH6" s="67"/>
-      <c r="AI6" s="67"/>
-      <c r="AJ6" s="67"/>
-      <c r="AK6" s="67"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+      <c r="Q6" s="69"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="69"/>
+      <c r="V6" s="69"/>
+      <c r="W6" s="69"/>
+      <c r="X6" s="69"/>
+      <c r="Y6" s="69"/>
+      <c r="Z6" s="69"/>
+      <c r="AA6" s="69"/>
+      <c r="AB6" s="69"/>
+      <c r="AC6" s="69"/>
+      <c r="AD6" s="69"/>
+      <c r="AE6" s="69"/>
+      <c r="AF6" s="69"/>
+      <c r="AG6" s="69"/>
+      <c r="AH6" s="69"/>
+      <c r="AI6" s="69"/>
+      <c r="AJ6" s="69"/>
+      <c r="AK6" s="69"/>
       <c r="AL6" s="40"/>
       <c r="AM6" s="40"/>
       <c r="AN6" s="40"/>
     </row>
-    <row r="7" spans="1:41" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1265,13 +1264,13 @@
       <c r="F7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="54">
         <v>1</v>
       </c>
-      <c r="H7" s="55">
+      <c r="H7" s="54">
         <v>2</v>
       </c>
-      <c r="I7" s="55">
+      <c r="I7" s="54">
         <v>3</v>
       </c>
       <c r="J7" s="6">
@@ -1280,19 +1279,19 @@
       <c r="K7" s="6">
         <v>5</v>
       </c>
-      <c r="L7" s="49">
+      <c r="L7" s="48">
         <v>6</v>
       </c>
-      <c r="M7" s="49">
+      <c r="M7" s="48">
         <v>7</v>
       </c>
       <c r="N7" s="6">
         <v>8</v>
       </c>
-      <c r="O7" s="55">
+      <c r="O7" s="54">
         <v>9</v>
       </c>
-      <c r="P7" s="55">
+      <c r="P7" s="54">
         <v>10</v>
       </c>
       <c r="Q7" s="6">
@@ -1301,72 +1300,72 @@
       <c r="R7" s="6">
         <v>12</v>
       </c>
-      <c r="S7" s="49">
+      <c r="S7" s="48">
         <v>13</v>
       </c>
-      <c r="T7" s="49">
+      <c r="T7" s="48">
         <v>14</v>
       </c>
       <c r="U7" s="6">
         <v>15</v>
       </c>
-      <c r="V7" s="55">
+      <c r="V7" s="54">
         <v>16</v>
       </c>
-      <c r="W7" s="55">
+      <c r="W7" s="54">
         <v>17</v>
       </c>
-      <c r="X7" s="55">
+      <c r="X7" s="54">
         <v>18</v>
       </c>
-      <c r="Y7" s="55">
+      <c r="Y7" s="54">
         <v>19</v>
       </c>
-      <c r="Z7" s="49">
+      <c r="Z7" s="48">
         <v>20</v>
       </c>
-      <c r="AA7" s="49">
+      <c r="AA7" s="48">
         <v>21</v>
       </c>
-      <c r="AB7" s="55">
+      <c r="AB7" s="54">
         <v>22</v>
       </c>
-      <c r="AC7" s="55">
+      <c r="AC7" s="54">
         <v>23</v>
       </c>
-      <c r="AD7" s="55">
+      <c r="AD7" s="54">
         <v>24</v>
       </c>
-      <c r="AE7" s="55">
+      <c r="AE7" s="54">
         <v>25</v>
       </c>
-      <c r="AF7" s="55">
+      <c r="AF7" s="54">
         <v>26</v>
       </c>
-      <c r="AG7" s="49">
+      <c r="AG7" s="48">
         <v>27</v>
       </c>
-      <c r="AH7" s="49">
+      <c r="AH7" s="48">
         <v>28</v>
       </c>
-      <c r="AI7" s="55">
+      <c r="AI7" s="54">
         <v>29</v>
       </c>
-      <c r="AJ7" s="55">
+      <c r="AJ7" s="54">
         <v>30</v>
       </c>
       <c r="AK7" s="6"/>
-      <c r="AL7" s="53" t="s">
+      <c r="AL7" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="AM7" s="53" t="s">
+      <c r="AM7" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="AN7" s="53" t="s">
+      <c r="AN7" s="52" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -1375,136 +1374,132 @@
       <c r="D8" s="30"/>
       <c r="E8" s="9"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
       <c r="U8" s="2"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="50"/>
-      <c r="AA8" s="50"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="56"/>
-      <c r="AE8" s="56"/>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="50"/>
-      <c r="AH8" s="50"/>
-      <c r="AI8" s="56"/>
-      <c r="AJ8" s="56"/>
+      <c r="V8" s="55"/>
+      <c r="W8" s="55"/>
+      <c r="X8" s="55"/>
+      <c r="Y8" s="55"/>
+      <c r="Z8" s="49"/>
+      <c r="AA8" s="49"/>
+      <c r="AB8" s="55"/>
+      <c r="AC8" s="55"/>
+      <c r="AD8" s="55"/>
+      <c r="AE8" s="55"/>
+      <c r="AF8" s="55"/>
+      <c r="AG8" s="49"/>
+      <c r="AH8" s="49"/>
+      <c r="AI8" s="55"/>
+      <c r="AJ8" s="55"/>
       <c r="AK8" s="2"/>
       <c r="AL8" s="3"/>
-      <c r="AM8" s="53"/>
-      <c r="AN8" s="53"/>
-      <c r="AO8" s="47">
-        <f t="shared" ref="AO8" si="0">50-AL8</f>
-        <v>50</v>
-      </c>
+      <c r="AM8" s="52"/>
+      <c r="AN8" s="52"/>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="68" t="s">
+      <c r="B9" s="53"/>
+      <c r="C9" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
       <c r="F9" s="41"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="69"/>
-      <c r="S9" s="69"/>
-      <c r="T9" s="69"/>
-      <c r="U9" s="69"/>
-      <c r="V9" s="69"/>
-      <c r="W9" s="69"/>
-      <c r="X9" s="69"/>
-      <c r="Y9" s="69"/>
-      <c r="Z9" s="69"/>
-      <c r="AA9" s="69"/>
-      <c r="AB9" s="69"/>
-      <c r="AC9" s="69"/>
-      <c r="AD9" s="69"/>
-      <c r="AE9" s="69"/>
-      <c r="AF9" s="69"/>
-      <c r="AG9" s="69"/>
-      <c r="AH9" s="69"/>
-      <c r="AI9" s="69"/>
-      <c r="AJ9" s="69"/>
-      <c r="AK9" s="69"/>
-      <c r="AL9" s="69"/>
-      <c r="AM9" s="69"/>
-      <c r="AN9" s="69"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
+      <c r="AA9" s="71"/>
+      <c r="AB9" s="71"/>
+      <c r="AC9" s="71"/>
+      <c r="AD9" s="71"/>
+      <c r="AE9" s="71"/>
+      <c r="AF9" s="71"/>
+      <c r="AG9" s="71"/>
+      <c r="AH9" s="71"/>
+      <c r="AI9" s="71"/>
+      <c r="AJ9" s="71"/>
+      <c r="AK9" s="71"/>
+      <c r="AL9" s="71"/>
+      <c r="AM9" s="71"/>
+      <c r="AN9" s="71"/>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="68" t="s">
+      <c r="B10" s="53"/>
+      <c r="C10" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
       <c r="F10" s="41"/>
-      <c r="G10" s="69" t="s">
+      <c r="G10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="69"/>
-      <c r="AA10" s="69"/>
-      <c r="AB10" s="69"/>
-      <c r="AC10" s="69"/>
-      <c r="AD10" s="69"/>
-      <c r="AE10" s="69"/>
-      <c r="AF10" s="69"/>
-      <c r="AG10" s="69"/>
-      <c r="AH10" s="69"/>
-      <c r="AI10" s="69"/>
-      <c r="AJ10" s="69"/>
-      <c r="AK10" s="69"/>
-      <c r="AL10" s="69"/>
-      <c r="AM10" s="69"/>
-      <c r="AN10" s="69"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="71"/>
+      <c r="U10" s="71"/>
+      <c r="V10" s="71"/>
+      <c r="W10" s="71"/>
+      <c r="X10" s="71"/>
+      <c r="Y10" s="71"/>
+      <c r="Z10" s="71"/>
+      <c r="AA10" s="71"/>
+      <c r="AB10" s="71"/>
+      <c r="AC10" s="71"/>
+      <c r="AD10" s="71"/>
+      <c r="AE10" s="71"/>
+      <c r="AF10" s="71"/>
+      <c r="AG10" s="71"/>
+      <c r="AH10" s="71"/>
+      <c r="AI10" s="71"/>
+      <c r="AJ10" s="71"/>
+      <c r="AK10" s="71"/>
+      <c r="AL10" s="71"/>
+      <c r="AM10" s="71"/>
+      <c r="AN10" s="71"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
         <v>16</v>
       </c>
@@ -1521,45 +1516,45 @@
         <v>16</v>
       </c>
       <c r="F11" s="16"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
       <c r="J11" s="16"/>
-      <c r="K11" s="63" t="s">
+      <c r="K11" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="63"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="63"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
+      <c r="N11" s="72"/>
+      <c r="O11" s="72"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="72"/>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
-      <c r="U11" s="63"/>
-      <c r="V11" s="63"/>
-      <c r="W11" s="63"/>
-      <c r="X11" s="63"/>
-      <c r="Y11" s="63"/>
-      <c r="Z11" s="63"/>
-      <c r="AA11" s="63"/>
-      <c r="AB11" s="63"/>
-      <c r="AD11" s="57"/>
-      <c r="AE11" s="65" t="s">
+      <c r="U11" s="72"/>
+      <c r="V11" s="72"/>
+      <c r="W11" s="72"/>
+      <c r="X11" s="72"/>
+      <c r="Y11" s="72"/>
+      <c r="Z11" s="72"/>
+      <c r="AA11" s="72"/>
+      <c r="AB11" s="72"/>
+      <c r="AD11" s="56"/>
+      <c r="AE11" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="AF11" s="65"/>
-      <c r="AG11" s="65"/>
-      <c r="AH11" s="65"/>
-      <c r="AI11" s="65"/>
-      <c r="AJ11" s="65"/>
-      <c r="AK11" s="65"/>
-      <c r="AL11" s="65"/>
-      <c r="AM11" s="65"/>
-      <c r="AN11" s="65"/>
+      <c r="AF11" s="73"/>
+      <c r="AG11" s="73"/>
+      <c r="AH11" s="73"/>
+      <c r="AI11" s="73"/>
+      <c r="AJ11" s="73"/>
+      <c r="AK11" s="73"/>
+      <c r="AL11" s="73"/>
+      <c r="AM11" s="73"/>
+      <c r="AN11" s="73"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="31" t="s">
         <v>16</v>
       </c>
@@ -1574,168 +1569,168 @@
       </c>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="63"/>
-      <c r="O12" s="63"/>
-      <c r="P12" s="63"/>
-      <c r="Q12" s="63"/>
-      <c r="R12" s="63"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="72"/>
       <c r="S12" s="16"/>
       <c r="T12" s="16"/>
-      <c r="U12" s="63"/>
-      <c r="V12" s="63"/>
-      <c r="W12" s="63"/>
-      <c r="X12" s="63"/>
-      <c r="Y12" s="63"/>
-      <c r="Z12" s="63"/>
-      <c r="AA12" s="63"/>
-      <c r="AB12" s="63"/>
-      <c r="AC12" s="57"/>
-      <c r="AD12" s="57"/>
-      <c r="AE12" s="64"/>
-      <c r="AF12" s="64"/>
-      <c r="AG12" s="64"/>
-      <c r="AH12" s="64"/>
-      <c r="AI12" s="64"/>
-      <c r="AJ12" s="64"/>
-      <c r="AK12" s="64"/>
-      <c r="AL12" s="64"/>
-      <c r="AM12" s="64"/>
-      <c r="AN12" s="64"/>
+      <c r="U12" s="72"/>
+      <c r="V12" s="72"/>
+      <c r="W12" s="72"/>
+      <c r="X12" s="72"/>
+      <c r="Y12" s="72"/>
+      <c r="Z12" s="72"/>
+      <c r="AA12" s="72"/>
+      <c r="AB12" s="72"/>
+      <c r="AC12" s="56"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="75"/>
+      <c r="AF12" s="75"/>
+      <c r="AG12" s="75"/>
+      <c r="AH12" s="75"/>
+      <c r="AI12" s="75"/>
+      <c r="AJ12" s="75"/>
+      <c r="AK12" s="75"/>
+      <c r="AL12" s="75"/>
+      <c r="AM12" s="75"/>
+      <c r="AN12" s="75"/>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="31"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="62" t="s">
+      <c r="G13" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="63"/>
-      <c r="O13" s="63"/>
-      <c r="P13" s="63"/>
-      <c r="Q13" s="63"/>
-      <c r="R13" s="63"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="72"/>
       <c r="S13" s="16"/>
       <c r="T13" s="16"/>
-      <c r="U13" s="63"/>
-      <c r="V13" s="63"/>
-      <c r="W13" s="63"/>
-      <c r="X13" s="63"/>
-      <c r="Y13" s="63"/>
-      <c r="Z13" s="63"/>
-      <c r="AA13" s="63"/>
-      <c r="AB13" s="63"/>
-      <c r="AC13" s="61"/>
-      <c r="AD13" s="61"/>
-      <c r="AE13" s="64"/>
-      <c r="AF13" s="64"/>
-      <c r="AG13" s="64"/>
-      <c r="AH13" s="64"/>
-      <c r="AI13" s="64"/>
-      <c r="AJ13" s="64"/>
-      <c r="AK13" s="64"/>
-      <c r="AL13" s="64"/>
-      <c r="AM13" s="64"/>
-      <c r="AN13" s="64"/>
+      <c r="U13" s="72"/>
+      <c r="V13" s="72"/>
+      <c r="W13" s="72"/>
+      <c r="X13" s="72"/>
+      <c r="Y13" s="72"/>
+      <c r="Z13" s="72"/>
+      <c r="AA13" s="72"/>
+      <c r="AB13" s="72"/>
+      <c r="AC13" s="60"/>
+      <c r="AD13" s="60"/>
+      <c r="AE13" s="75"/>
+      <c r="AF13" s="75"/>
+      <c r="AG13" s="75"/>
+      <c r="AH13" s="75"/>
+      <c r="AI13" s="75"/>
+      <c r="AJ13" s="75"/>
+      <c r="AK13" s="75"/>
+      <c r="AL13" s="75"/>
+      <c r="AM13" s="75"/>
+      <c r="AN13" s="75"/>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="31"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="62" t="s">
+      <c r="G14" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
       <c r="K14" s="12"/>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
+      <c r="O14" s="58"/>
+      <c r="P14" s="58"/>
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
       <c r="T14" s="12"/>
       <c r="U14" s="19"/>
-      <c r="V14" s="60"/>
-      <c r="W14" s="59"/>
+      <c r="V14" s="59"/>
+      <c r="W14" s="58"/>
       <c r="X14" s="12"/>
-      <c r="Y14" s="59"/>
+      <c r="Y14" s="58"/>
       <c r="Z14" s="12"/>
       <c r="AA14" s="12"/>
       <c r="AB14" s="12"/>
-      <c r="AC14" s="59"/>
-      <c r="AD14" s="59"/>
-      <c r="AE14" s="59"/>
-      <c r="AF14" s="60"/>
-      <c r="AG14" s="60"/>
-      <c r="AH14" s="60"/>
-      <c r="AI14" s="60"/>
-      <c r="AJ14" s="60"/>
+      <c r="AC14" s="58"/>
+      <c r="AD14" s="58"/>
+      <c r="AE14" s="58"/>
+      <c r="AF14" s="59"/>
+      <c r="AG14" s="59"/>
+      <c r="AH14" s="59"/>
+      <c r="AI14" s="59"/>
+      <c r="AJ14" s="59"/>
       <c r="AK14" s="19"/>
       <c r="AL14" s="12"/>
       <c r="AM14" s="12"/>
       <c r="AN14" s="20"/>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="21"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
       <c r="D15" s="24"/>
       <c r="E15" s="25"/>
       <c r="F15" s="22"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
       <c r="N15" s="13"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="58"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="57"/>
       <c r="Q15" s="13"/>
       <c r="R15" s="13"/>
       <c r="S15" s="13"/>
       <c r="T15" s="13"/>
       <c r="U15" s="13"/>
-      <c r="V15" s="58"/>
-      <c r="W15" s="58"/>
+      <c r="V15" s="57"/>
+      <c r="W15" s="57"/>
       <c r="X15" s="13"/>
-      <c r="Y15" s="58"/>
+      <c r="Y15" s="57"/>
       <c r="Z15" s="13"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="13"/>
-      <c r="AC15" s="58"/>
-      <c r="AD15" s="58"/>
-      <c r="AE15" s="58"/>
-      <c r="AF15" s="58"/>
-      <c r="AG15" s="58"/>
-      <c r="AH15" s="58"/>
-      <c r="AI15" s="58"/>
-      <c r="AJ15" s="58"/>
+      <c r="AC15" s="57"/>
+      <c r="AD15" s="57"/>
+      <c r="AE15" s="57"/>
+      <c r="AF15" s="57"/>
+      <c r="AG15" s="57"/>
+      <c r="AH15" s="57"/>
+      <c r="AI15" s="57"/>
+      <c r="AJ15" s="57"/>
       <c r="AK15" s="13"/>
       <c r="AL15" s="13"/>
       <c r="AM15" s="13"/>
@@ -1745,9 +1740,9 @@
       <c r="C17" s="43"/>
       <c r="E17" s="43"/>
       <c r="F17" s="10"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
     </row>
@@ -1758,18 +1753,11 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:AN2"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:AK5"/>
-    <mergeCell ref="AL4:AN5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="G6:AK6"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="G9:AN9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="G10:AN10"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="K13:R13"/>
+    <mergeCell ref="U13:AB13"/>
+    <mergeCell ref="AE13:AN13"/>
+    <mergeCell ref="G14:J14"/>
     <mergeCell ref="K11:R11"/>
     <mergeCell ref="U11:AB11"/>
     <mergeCell ref="AE11:AN11"/>
@@ -1777,11 +1765,18 @@
     <mergeCell ref="K12:R12"/>
     <mergeCell ref="U12:AB12"/>
     <mergeCell ref="AE12:AN12"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="K13:R13"/>
-    <mergeCell ref="U13:AB13"/>
-    <mergeCell ref="AE13:AN13"/>
-    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="G6:AK6"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="G9:AN9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="G10:AN10"/>
+    <mergeCell ref="A1:AN2"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:AK5"/>
+    <mergeCell ref="AL4:AN5"/>
+    <mergeCell ref="C5:E5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.31496062992125984" bottom="0.27559055118110237" header="0.51181102362204722" footer="0.51181102362204722"/>
